--- a/input/targets_curated.xlsx
+++ b/input/targets_curated.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominicgoj/coding/pichai/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominicgoj/coding/pichai/autoplasmid/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7489E553-6D12-314F-8FF3-C9A86C426105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45A2E30-6035-8745-964D-A4E9D08A0B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10960" yWindow="-28200" windowWidth="51200" windowHeight="28200" xr2:uid="{AE8E4A6F-4344-5045-863F-544E56AE9E4F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>seq_id</t>
   </si>
@@ -47,10 +47,134 @@
     <t>gene_seq</t>
   </si>
   <si>
-    <t>IbChitinase</t>
-  </si>
-  <si>
-    <t>CAAGGTGTAGGCTCTATTGTCACGAAGCCCTTATTCGATGAGATGCTTAAACATAGAAATGACGCTAACTGCGCATCAGGTTTTTACACTTACGAGGCATTCATACAGGCAGCTAATTCATTCGCTGCATTTGGAACAGCCGGAGATGTCGATACCAGAAAGAGAGAAATTGCCGCCTTCCTTGCACAGACTTCTCACGAAACGACGGGTGGTTGGGCTACTGCTCCAGATGGTCCATATGCCTGGGGATATTGTTTTAAACAAGAACAAGGAAACCCACCTGATTACTGTCAGGCTAGTCAAGAGTGGCCCTGTGCTCCAGGCAAGAAATACTTTGGTAGAGGTCCAATTCAGATTTCTTACAACTTTAACTATGGCCCCGCCGGCAAGGCAATTGGTAGTGATCTACTGAATAATCCTGACCTAGTTGCCACTGACCCAGTTATCTCTTTTAAAACTGCTTTTTGGTTTTGGATGACCCCACAGAGTCCAAAACCTTCAGCACATGCTGTTATGACAGGTGGATGGACACCATCTGCCGCCGATACCGCTGCTGGTAGAGTTCCAGGATACGGAGTTGTTACGAATATCATCAATGGAGGTATTGAGTGCGGTAAGGGCTCCAACCCACAAATGGAGGACAGAATCGGTTTTTACAAAAGGTATTGCGATATCTTGGGAGTTGGTTACGGTAACAACCTAGACTGTGCAAACCAAAGGCCATTTGGATCT</t>
+    <t>ATTAAACTAATCGTTAATGCAGATGATTTCGGTCTGACCGAGGGAACTAACTACGGAATCATCGACGGCCATATTAATGGACTGGTCAACTCTACTACCATGATGATGAACATGCCTGGAACCGAACATGCTGTTCATTTGGCTAAGGAATATAAGACTCTGGGTGTTGGAGTTCACTTGGTACTAACTGCCGGAAAGCCACTTCTTGGTGATGTCCCATCACTGGTTTCTTCTGATGGATTGTTCCACAAACAATCTGTGGTTTGGGAGGGTAAGGTGAATCCAGAGGAGGTTGAACGTGAGTGGACGGCTCAAATTGAAAAATTTCTTTCTTATGGCTTAAAACCAACTCACCTAGATTCACACCATCACGTTCATGGTTTACCCATACTACACGATGTGCTTGAACGTTTGGCAGCAACCTATAATGTTCCAATCAGAAGATGTGAGGAAGAAAGAGCCGTGAGACCATTTTCAGATTTGTTCTATTCAGACTTTTATGCTGATGGAGTGACTGAGGACTATTTTGTAAAGTTGAAGGAACGTGTGCAAGGTGAGCAAACAGTGGAGATTATGGTTCACCCAGCTTATATCGATCCTGAATTGGTGAAGAGAAGTTCCTACGTGATGGACAGAGTTAAAGAGCTAAGAATTTTGACAGAATCCGAATTGCCAGAGGGAATTGAATTGGTGAAATTT</t>
+  </si>
+  <si>
+    <t>CTGATAGAAAGTAAGCAGAGTTCATTGACAATTGAAAATTCTGAACGTCCAATTTTGTCTAGACTGCTGCTTCCACTAATAATAGCAGTTACAGCCTTGTTGAGTGCCTGCGTGGGTGGCTCATCTTCCACAGCTAAGGATCCTATTGACACCACCCCTATCTCTAGTGGATCTAGTGACTCAACTGACAATTCCTCTAATAATGACAGTGTGAACGGAGAAGTGAGTCGTGCAAACATTTTACTTGGAGGTGTGGAATATCAACCAATTCTGGACGAATTGGCCTTGCCAACCTACTGGGCCGCCACCTCTGAGCCATCCGAAGAGATGCTGTCAGTTTTAAATACTCAATTGGCTCCCCTATCAGATACTTTTTCTTCTCAATTTACCTTAGAGTCTTTTGCTCTTGGACTGAAACTTGATCCACTGCAATCTCAAGCTTACAAAATCGACATCTCTACGTCTGAATTGGGCCAGTCTAGAGTAATCTTGACCCTTGTAGCCGTGCCACAAGATGGCGTTCTTACTCAACCATTGGCTACCGCTATTTACATAGCTTTACGTCAGGCACACCAAGCTGAAGGTGGACTGTTGGGTAAGTTGGTCAATCACGGTCTAGCTCTGCACTTCATAGAGTCCGAGCTTAAGCCTGCTCACTTGTACCAAGAGACAGAGTTAACTGGAACCGCATTGGATGATGCAATTACTCAAGCCAAGTCAGCAATTAAAAATGAAACTGACAATGGTACCGGCGATGATGCTTGGTTTAACGGTGCTGAACCCAAGGATAACGGCGTCGCATGGAAGCTTGGTTACTACTTGGTTGCTCAACATTTCGTTAGATACCCCGGCTCAGACGCAGCAAACTCCTTCGCCCTTGATCCTGGACTTTTCAGAATCAATCTAGCTTCTCCTATTACTGTGAATCACAAAAATGAACAATATGTACGTACAGGCGATGTCGCAAACCAAGTCGGAATTAGTGAGTTAACTCGTCAAGCTAGTGACTACATAGGTGCATATTTCTTAGAGGGATGGAATCAGGACAAGCTTATTGCCCTTACCTTCGATGACGGACCATCAATTTACACCACACAGATCTTGGATCTGTTAGCACAGTACCAAATCCCTGCTTCATTCTTTTGGATGGGTAAGAACATGCAATCTAATCAAGCTATAATGGCTAGAGCCCTTGCAGAAGGTCACACTCTTGCTAACCACTCCTGGAATCACCCTCATGGTCGTAGTTTGACTTCTGAGGATCTTTGGCAAACGCAAATATTGAAAACAAACGAACTTTTTCAATCTTCTGTTGGAATTACCCCAAGATTCTACAGGCCACCTTATGGAGAGATTACCGGAAAACAAGTAGCTTTCTTAGATGACAAGGGTATAAAGGTCATCCTTTGGTCAGTTGACACACGTGACTGGAACTCCCCTCTTGTTACTGTCGAAAACATCTCAGACGTTATGATTAATAACCAACACCCTGAAGTTATTAGTCTAATGCACGACGCTGGAGGCAACCGTCAAAACACTGTAGACGCACTGCCTGGAGTTATAGACTATTACCATACCCAAGGCTATCGTTTTGTCAATTTAGAGATCATGCTGGGAATTTCCGACAAGAGA</t>
+  </si>
+  <si>
+    <t>TCTGATTTATCCCCAGCTGCCGCCGCACAAGCAGATATTACTATGCATTCTGGCGCATCCGATCAGTATCAGGCCAAAGCTCTTATAAGTAAATCTAGTGAATTTATTATTATTGGTGAATTTACTAACTCTCTAAATGAACACTGGTTGAGGATCAAATATGACGGTGAAACTGGATGGATCAAGGATACAGGCATTCGTCGTATGGACTTGAACGCTCAGTATTTAACTTCTAGTGCTGCTAACACACCTATCAGAAGGGGAGCTTCCCTTTCTTACCAACACACTGGTGATCTTAAGCATGGAGTAATGGTTAAGATAATTGATACTTTTATAAGAGAAAACGGAGAAATTTGGGTAAGATTGAGTAATGGTAACGTTACCGGCTGGTCTAGATTGCAGGACCTTGAGTTATTTGAGGGTACGAAAAACTATTTGAACAAACCAGTTTTCGTCAAATCTGATACACAAGTTAAACGTGGAGCTTCTTCAGCTGCCAAAGCCGTTTATACGTTGAAAAAGGGTAAAGAAGTTACCATCCAGTCCACACTTATCAATGGAAAAGAAGTTTGGCACCGTATCGCTGATGGAAAGAGAACTGGATGGGTCCCTGCAGACAGTGTGGCTAATCAGGTGAACTACTCCGCTTATATGTATGTTAAAGATCAGTCAGCTGCTATCAGAAGAGGTGCCTCCGCTTCCTACAAAACTGTGTCAAACTTGACTTATGGTCAACAAGTTAAGATTACCAGTGAGTTTATGAACGGTAGTGGTGATGTATGGTACAAGGTCTCTGCAGGTAAGGGATTGGAGGGATGGATTCCTGGCAAGTCTGTCACTTCAAGACCAATGAAAGTTGCTTATTTGACAATTGACGATGGTCCTACGGTCTATACGAACAAGCTACTTGATGCATTGAACCAATACGATGCTAAAGCCACTTTTTTTATGGTAAATGGCAATATCAACACATACCCCAAGGCTGTCAAAAGAATGGTTGCTGAAGGACACGCCGTCGGTTCCCACAGTGTTACTCACGACAAGAATAAATTCTACAGGTCACCTGCAGCAGCAGTGAGTGAGATGAAGACTACCAGAAACTCAATCAAGAAGGTTACAGGAGTTACTTCTAATCTGATTAGAACTCCCTATGGTTCTATTCCTTACATGAAGCAGAATTACAGAAATGCAATGACCAAAGAGTACTTCATTATGTGGGATTGGAACGTCGACAGTTTGGATTGGAAGTTCAACTCCTCATCATATGTTAATTACACTTTGCATTACGTGGATATGCAGGAAAAAAAGGGACAGGCCCCAATTATTTTGATTCACGATAGAAAGGCTACCGTTAACGCACTACCTTCTTTATTATCTCAGTTGAAAAAGCGTGGTTATGTTCTGGCCCCTCTGAACGAATCAATGACGCCACATCAATTCAAATTGAAG</t>
+  </si>
+  <si>
+    <t>CCTAACGGTATGAATCCAAAAAACGTTCCCCAAATGATAACTATTACATTTGATGACGCAGTCAACACAGGTAATATTGATCTTTACGAGGAACTGTTTGGTAACCAAACCTTATTAAATCCAAATTCTTGTGCAATTAAGGGAACATTTTTTGTTAGTCACAAGTACTCTAACTATTCCGCAGTTCAAGAGTTGCACAGGCTAGGTCATGAGATCGCCGTTCATTCTATTTCACATAATTCTAGTACCGACTTTTGGACCTCCGCTACTGAGGAACAATGGACCCAAGAGATGGCCGGAGCAAGGGTAATATCAGAAAGATTTGCTAACATCACTGATCAAAGTATCATCGGAATGAGAGCTCCATTCAACAGAGTTGGTTCAAATAAACAATTCAAGATGATGGAAGACCAGGCTTTTCTGTACGATTCTAGTGTCAACGCTCCACTTGGTAAAGTTCCACATTGGCCCTACACCCTATACTATAGAATGCCACATCCTTGTCACGGACATCTTCAAGAGTGCCCAACTCGTTCTTTTGCCGTTTGGGAGATGGTCATGAACGAAATGGACAGAAGAGAAGATCCTGAGTTTGAAGAGCCACTACCTGGTTGCGTCATGGTGGATTCATGCTTCTCTTCTAAACCTTCTGGTGATCAGTTTTATAAGTTCTTGACTAACAATTTCGACCATCATTACAACACTAACCGTGCCCCATTGGGACTTTTCTTCCAATCTGCTTTTTTGAAAAATAACCACGAGGTGAGAGAGAACTTTTTGCGTTGGATAAAGGAGATTCTGGCAACCCACAATGATGTTTATTTCGTTACAATGACCCAAGTTATTCAGTGGATGCAAGACACCCGTTCTGTCAACGAATTGCCTAATTTCGGCCCATGGAAGGATAAATGTATTGTCCAGGGACAACCTATGTGTAATGGTGGTAACAACTGTGAACTGAATACTCAAGATTTGCCAGGTGAAACCTTGTTTCTACCTACTTGCATGACATGTCCCAATAACTACCCATGGTTGCAAGACCCAACTGGTGAAGGATACTTT</t>
+  </si>
+  <si>
+    <t>GCTTTCATTCCTTACACCAACGATAGATTCAGACTACATTCAAGAAGTAACTCTTCTAGTACGGGTTTCAGATCCGTCGCATATTTCGTTGATTGGGCTATTTACGCTAGGAACTTTAACCCCCAAAACTTGACTACTGAAACGTTGACTCATGTTTTATATGCATTTGCAAACGTTGATCAAAATACAGGAGAGGTGTCATTGGCTGACACATACGCTGATATCCAAAAGCATTATCCTACCGACTCTTGGAATGAACAGGGTAACAACGTTTATGGCTGCGTTAAACAATTATTTCTTCTGAAAAAAAAGCAAAGAAACCTGAAGACACTGTTATCCATCGGAGGTTACACATACAGTCCTAAATTTTCTACTTTCACTACGACTGAATCTGGCAGGCAAACCTTCGCTAGTACAGCAGTTCAAATGGTGCAAAATTTGGGCTTTGACGGTATCGACATTGACTGGGAATACCCCAACAATGCAACCGAGGCCGACAACATGGTGGCATTGTTGAAAGACGTTAGGGAAGCATTGGACAACTACTCAGCAAAATACGCTAACGGAACTCATTTATTACTTTCCGTAGCTTCCCCAGCAGGCCCATCAAATTATCAGCCAATGCATTTAGCTGAAATGGATCAATATCTGGATTTCTGGAACCTTATGGCCTACGATTACACGGGATCTTGGTCTACAGTTGCTGGCCATATGGCAAATGTGTTTCCCTCTACTTCTAACCCTGCCTCAACCCCTTTCAACACAGACCAGGCTGTTTCTTACTACACTTCTAACGGTGTGGCACCATCCAAGATCAATTTGGGTATTCCATTGTATGGAAGGTCCTTCTTGCAGACAGATGGACCAGGAACTGCCTACAATGGAGTTGGACCCGGCGAATGGGAGGGTGGTCCAGGCGTCTGGGACTACAAAGCCCTGCCACAGGCTGGTGCTACCGTTTACGAGCTGGATCAGCCAATCGCCTCTTATTCTTACGACCCCAACCAGAAGATTATGATATCATATGATACTCCTAACGTGGTCGCATGGAAGGGAGATTATATTCAGCAGAAGGGTATTGGCGGCGGTATGTATTGGGAATCTTCAGGAGATAAGTCCGGAAACGAATCTTTAATCGCTACTCTTGTAAACAGAGTCGGAGGAACAGCAGTGCTGGACCAAAGTCCAAACCTATTGTCATATCCTGCTTCTATTTACGACAATCTGAGGGCTGGATTCCCTTCCAAT</t>
+  </si>
+  <si>
+    <t>AGACAAGTTCCTGTTGGTACACCCATTCTACAATGCACCCAGCCAGGTCTGGTTGCTTTGACTTATGACGACGGTCCATTCACATTCACTCCACAATTGTTGGATATCTTGAAGCAAAACGATGTAAGGGCAACTTTCTTTGTGAACGGCAATAATTGGGCTAACATAGAGGCCGGATCTAACCCAGATACAATTAGGAGAATGCGTGCTGATGGACATTTGGTAGGCTCTCACACTTATGCCCATCCTGATTTGAACACCCTATCCTCAGCAGACCGTATATCACAGATGCGTCATGTAGAAGAAGCAACTAGGCGTATTGATGGCTTCGCCCCTAAATACATGAGAGCCCCATACTTATCTTGTGATGCCGGTTGTCAAGGTGATCTTGGTGGTCTTGGTTACCACATCATTGATACCAATTTGGACACTAAGGATTACGAAAACAACAAGCCAGAGACTACGCATTTGTCAGCAGAAAAGTTCAACAACGAATTGTCCGCCGACGTGGGTGCTAATTCATATATAGTCCTATCTCATGACGTTCACGAACAGACTGTGGTATCCTTGACACAAAAGTTGATTGACACTCTGAAAAGTAAGGGATATAGAGCTGTTACCGTAGGAGAATGTCTTGGAGATGCCCCAGAAAATTGGTACAAAGCA</t>
+  </si>
+  <si>
+    <t>TCACCAATTACTAGAGAGGAAAGATTGGAGCGTAGAATCCAAGACCTTTACGCCAACGATCCTCAGTTCGCCGCCGCTAAGCCAGCTACAGCTATTACCGCTGCTATTGAAAGACCAGGACTACCTTTACCTCAAATCATTGAGACCGTCATGACTGGTTACGCAGATAGGCCAGCACTGGCTCAGAGATCAGTTGAATTTGTGACTGACGCCGGAACGGGACATACTACTCTGCGTCTGCTTCCACACTTTGAAACCATCAGTTACGGTGAGCTTTGGGACAGAATATCTGCCCTAGCTGACGTTCTTTCTACCGAACAAACCGTCAAACCCGGAGATAGAGTTTGCTTGCTGGGATTTAATAGTGTTGATTACGCAACCATTGATATGACCCTTGCTAGGTTGGGTGCAGTGGCCGTTCCTTTACAGACTTCCGCCGCTATTACGCAGTTGCAGCCCATTGTGGCCGAGACACAACCAACTATGATTGCAGCATCCGTTGACGCTCTGGCCGATGCTACGGAATTGGCCCTATCTGGCCAGACAGCAACCAGGGTTCTGGTTTTTGACCATCACCGTCAGGTAGATGCTCATAGAGCCGCAGTGGAATCTGCTAGAGAAAGATTGGCTGGTTCTGCAGTTGTTGAGACATTGGCTGAGGCTATTGCCAGAGGTGATGTGCCTCGTGGTGCATCCGCAGGTAGTGCTCCTGGCACAGATGTTAGTGACGATTCTTTGGCTTTATTAATCTATACCAGTGGTTCCACTGGAGCCCCTAAAGGCGCAATGTACCCAAGACGTAACGTTGCTACTTTCTGGAGGAAGAGGACTTGGTTTGAAGGTGGCTATGAACCATCCATTACCTTAAATTTCATGCCAATGTCCCATGTTATGGGTAGACAGATTCTATACGGAACTTTATGTAATGGAGGTACTGCCTACTTTGTAGCTAAATCAGACTTGAGTACCTTATTTGAGGATTTAGCTCTGGTTAGACCAACGGAGCTGACTTTCGTACCAAGAGTCTGGGACATGGTTTTTGACGAGTTCCAAAGTGAGGTCGACAGACGTTTGGTGGATGGCGCCGATAGAGTCGCTCTAGAGGCCCAAGTTAAAGCAGAAATAAGAAACGACGTTTTGGGCGGAAGATATACTTCTGCTCTGACCGGATCTGCCCCTATCAGTGATGAGATGAAAGCTTGGGTCGAGGAACTGCTGGACATGCACCTAGTTGAGGGATATGGATCTACCGAAGCAGGAATGATACTTATAGATGGCGCTATTAGGAGACCTGCTGTATTGGATTATAAGCTTGTTGACGTCCCAGACCTGGGATACTTTCTTACGGACAGACCACATCCTAGGGGAGAGTTATTGGTGAAGACTGATTCATTGTTTCCTGGTTACTACCAGAGAGCAGAGGTAACAGCCGACGTTTTCGACGCCGATGGCTTCTATAGAACAGGTGACATTATGGCTGAAGTTGGACCAGAGCAGTTCGTATATTTAGATCGTAGAAATAACGTTTTGAAGTTAAGTCAGGGAGAATTCGTTACAGTATCAAAGCTTGAAGCTGTCTTCGGAGACTCTCCATTGGTTAGGCAGATTTATATCTACGGTAATTCCGCTAGGGCCTATTTGTTGGCTGTTATCGTTCCCACTCAAGAAGCCCTGGATGCCGTGCCTGTAGAGGAATTGAAAGCCAGGTTGGGTGATTCTTTGCAAGAGGTCGCTAAAGCAGCTGGACTACAATCTTACGAAATCCCTCGTGATTTCATTATCGAAACCACCCCATGGACATTGGAGAACGGTCTTCTTACAGGAATAAGAAAGCTGGCTAGACCTCAATTAAAAAAGCATTATGGTGAATTGTTAGAACAGATCTACACTGACCTAGCCCATGGACAGGCAGATGAGTTAAGGTCACTTCGTCAGTCAGGTGCAGATGCCCCAGTGCTAGTTACTGTTTGTAGAGCCGCTGCAGCCCTGTTGGGAGGATCCGCAAGTGACGTTCAACCTGATGCACATTTTACCGATCTGGGCGGTGACTCATTGTCAGCCCTTAGTTTTACTAATCTACTTCACGAGATCTTCGATATAGAGGTACCAGTGGGTGTCATCGTTTCACCAGCAAACGACTTACAAGCATTGGCTGATTACGTAGAAGCCGCCAGGAAACCAGGATCATCAAGACCAACGTTCGCTAGTGTACATGGTGCTTCTAACGGACAAGTAACTGAAGTACACGCCGGTGACCTAAGTCTGGATAAGTTTATTGATGCTGCAACCCTTGCAGAGGCCCCAAGATTGCCTGCAGCTAACACTCAGGTAAGAACGGTTCTATTGACCGGTGCTACCGGCTTTTTAGGCAGATATTTGGCCCTTGAATGGTTGGAAAGAATGGATCTAGTCGATGGAAAGTTGATTTGCCTAGTTCGTGCCAAATCTGACACAGAAGCTAGGGCCAGGTTGGACAAAACCTTCGATAGTGGTGACCCTGAGTTGCTGGCCCACTACCGTGCTCTGGCCGGTGATCACTTGGAGGTTCTGGCTGGTGACAAAGGTGAGGCTGATTTGGGATTAGACAGACAAACATGGCAAAGGTTGGCTGATACTGTTGACCTAATTGTTGATCCTGCCGCACTAGTTAATCATGTGCTTCCATACTCACAATTGTTTGGTCCAAATGCACTTGGTACAGCAGAACTTTTGAGACTGGCCTTGACATCAAAAATTAAACCCTACTCTTATACCTCAACAATAGGAGTTGCCGACCAGATCCCACCCTCTGCCTTCACGGAGGACGCCGATATTAGGGTCATTTCCGCTACAAGGGCTGTGGATGACTCTTACGCCAATGGTTATTCTAACTCCAAATGGGCTGGCGAAGTTTTGTTGAGAGAGGCACACGACTTGTGTGGATTACCTGTGGCCGTTTTTAGATGCGACATGATATTGGCCGACACCACTTGGGCTGGACAGTTGAATGTGCCTGATATGTTTACGAGAATGATCCTATCTTTAGCAGCTACTGGCATTGCCCCAGGTAGTTTTTATGAATTAGCTGCCGACGGTGCCAGGCAAAGGGCTCATTATGACGGTCTGCCAGTGGAATTTATTGCAGAAGCTATATCTACTTTAGGCGCCCAGTCACAAGATGGATTTCACACTTACCATGTTATGAACCCATATGATGACGGCATCGGATTGGATGAGTTTGTCGATTGGTTGAACGAATCCGGATGTCCAATTCAAAGAATTGCCGATTATGGAGACTGGTTGCAGAGGTTCGAAACAGCTCTTAGAGCTCTACCTGATAGACAGCGTCACTCTTCATTACTGCCTTTGCTTCATAACTATAGACAACCAGAAAGGCCAGTGAGAGGTAGTATTGCACCAACAGACCGTTTCAGAGCTGCTGTGCAGGAAGCCAAAATTGGTCCTGATAAAGATATACCTCATGTTGGTGCCCCTATTATTGTGAAGTATGTTTCTGATTTGAGGCTTCTAGGTTTGTTA</t>
+  </si>
+  <si>
+    <t>TCTCAACAGCAAAACCCCCCCTATGGTAGACGTTTAATATTAGATATTATTAAAGAAAGGGCCCTTAATGAACCTAATAGGGAGTGGGTATCTGTTCCAAGGTCATCTGATCCCAAAGACGGCTGGAAGATATTAACCTACCTAGACGCATACAACGGCATCAATCGTGTAGCCCATAAGCTGACGCAGGTCTGTGGAGCAGCAGCCCCTGGCTCTTTTCCCACTGTAGCTTATATCGGCCCTAATGATGTGAGGTATCTTGTATTTGCTTTGGGCGCAGTTAAAGCAGGTTACAAAGCACTTTTTATTTCCACGAGGAATAGTGCTGAGGCCCAAGTAAACCTGTTCGAGTTGACAAACTGCAACGTGCTTGTTTTTGATCAAAGTTACAAAGCTACCGTGCAGCCATGGCTACACGAGAGGGAAATGACAGCAATTCTAGCCCTTCCCGCTGATGAATGGTTTCCTGCAGACCAAGAGGACTTCCCATATAACAAGACATTTGAGGAGGCTGAGTGGGACCCTCTTATGGTACTGCATACCTCAGGATCTACTGGTTTCCCAAAACCAATTGTAGCCAGACAAGGTATGCTGGCCGTCGCCGACCAATTTCACAACCTACCCCCCCGTGAAGATGGTAAGTTAATGTGGATTGTAGAGATGTCAAAACGTGCTAAGAGATTGATGCATCCAATGCCATTATTCCACGCCGCCGGTATGTACATATCAATGTTGATGATACACTATTGGGACACCCCCGGCGCCCTAGGTATAGGCGAAAGACCCCTTTCCTCAGACCTGGTGCTTGACTACATAGAGTACGCCGACGTTGAGGGTATGATCCTGCCACCCGCAATACTGGAGGAGCTATCCAGGGACGAGAAAGCCATCCAATCACTGCAAAAGTTGAACTTTGTATCATTCGGTGGCGGCAATCTTGCACCTGAAGCCGGAGACAGGCTGGTTGAGAATAACGTCACTCTGTGCAACCTTATATCTGCCACAGAGTTCACCCCCTTCCCATTTTACTGGCAATATGATCAAAAGTTGTGGAGGTATTTCAATTTTGATACAGACCTATTCGGCATAGATTGGAGGCTTCACGATGGTGAGTCCACGTATGAGCAGGTGATAGTGAGAAAAGATAAGCACCCAGGCTTGCAAGGCTTTTTCTACACATTCCCAGATTCCTCCGAGTACTCCACCAAAGATTTATATAAGAGGCACCCTACCCATGAAGATTTTTGGATCTACCAGGGAAGGGCTGATAATATCATAGTGTTCAGTAATGGTGAAAAACTTAATCCTATTACTATTGAGGAGACCTTACAAGGTCATCCAAAGGTGATGGGCGCTGTGGTGGTCGGTACTAACAGGTTCCAGCCAGCATTAATTATTGAACCTGTGGAGCACCCTGAGACTGAGGAAGGCAGGAAAGCTCTGCTTGATGAGATATGGCCTACCGTTGTGCGTGTAAACAAAGAGACCGTCGCTCATGGCCAAATCGGAAGACAGTACATGGCCCTAAGTACCCCAGGCAAACCCTTTCTACGTGCCGGAAAGGGTACCGTATTGAGGCCAGGTACCATCAATATGTATAAAGCTGAAATAGATAAAATCTACGAAGATGCTGAAAAGGGTGTCGCAACCGATGAAGTGCCTAAGTTGGATCTATCTTCTTCTGATGCTCTTATAGTCTCCATTGAGAAACTTTTCGAGACGTCTTTAAATGCTCCTAAACTGGAGGCCGATACGGACTTTTTTACCGCTGGTGTTGACTCAATGCAAGTAATTACCGCAAGTAGACTGATTAGGGCCGGTCTGGCCGCTGCCGGCGTCAACATCGAAGCATCTGCCTTGGCTACGAGGGTGATCTACGGTAACCCTACGCCTAAAAGGCTTGCAGACTACTTATTGTCCATCGTGAATAAGGACTCTAATCAGGGTACTTTAGACAATGAACACCATGTCATGGAGGCCCTTGTCGAAAAATATACGAGAGATTTACCCACCCCTAAGCAAAACAAGCCAGCCCCAGCCGACGAAGGCCAAGTGGTGGTAATCACAGGCACCACTGGAGGAATAGGTTCCTACCTTATAGACATCTGTTCAAGTTCAAGTCGTGTATCCAAGATAATATGTCTGAACCGTTCTGAGGATGGCAAAGCCCGTCAAACCGCATCCTCTTCTGGCCGTGGCTTATCCACCGATTTTTCTAAATGCGAATTTTACCACGCCGATATGTCTAGGGCAGATCTTGGACTGGGTCCAGAGGTTTATAGTCGTTTACTGTCAGAAGTAGACAGGGTCATACATAATCAATGGCCTGTCAACTTCAATATTGCCGTCGAATCATTCGAACCTCACATCAGAGGTTGTCGTAACTTAGTTGACTTCTCCTATAAGGCCGACAAAAACGTCCCTATAGTTTTCGTTTCTTCTATCGGTACGGTTGATAGGTGGCATGACGAAGATCGTATTGTGCCAGAAGCCTCACTTGATGATCTGAGTCTGGCCGCTGGTGGCTATGGACAGTCTAAGTTGGTAAGTTCCTTGATCTTCGATAAGGCCGCTGAGGTTTCTGGCGTCCCCACGGAGGTGGTACGTGTGGGTCAAGTGGCAGGCCCATCATCAGAGAAGGGATACTGGAACAAACAAGAATGGCTACCATCCATAGTTGCTTCTTCCGCCTATCTTGGTGTGCTTCCTGATTCCTTGGGACAGATGACTACAATAGACTGGACGCCAATTGAAGCTATCGCAAAACTACTTTTAGAAGTTTCCGGCGTCATAGACAATGTGCCTCTAGACAAGATAAACGGTTACTTCCACGGAGTCAACCCTGAAAGGACTTCCTGGTCTGCTCTGGCCCCCGCAGTACAGGAGTATTATGGTGACAGGATTCAAAAAATCGTACCACTAGATGAATGGTTGGAGGCATTAGAGAAGTCTCAAGAAAAGGCAGAAGACGTGACACGTAATCCTGGTATAAAACTTATAGACACTTACCGTACCTGGTCCGAGGGCTATAAGAAGGGCACGAAATTTGTGCCTCTTGACATGACTAGGACAAAGGAGTACTCCAAGACTATGCGTGAGATGCATGCAGTCACACCCGAATTGATGAAGAACTGGTGTCGTCAGTGGAACTTT</t>
+  </si>
+  <si>
+    <t>TCTAACGGTTCTACTGCTTTGATGGGTGAGGTTGACATGCAAACACCATTCCCTGAATGGTTGACTGAATTCACTAATTTGACTCAGTGGCCAGGAATTGACCCTCCCTATATCCCACTAGACTACATTAACCTTACTGAGGTTCCTGAGTTAGATAGATATTATCCAGGTCAATGCCCTAAAATCTCTAGAGAGCAATGTTCTTTTGACTGCTACAACTGCATAGATGTTGATGATGTCACTTCTTGCTTTAAGTTGAGTCAAACATTTGATGATGGTCCAGCCCCAGCTACCGAGGCCTTACTTAAAAAGCTAAGACAGAGAACGACTTTCTTTGTTTTGGGAATTAATACTGTCAACTACCCTGATATCTATGAACATATTCTAGAAAGGGGCCACCTGATTGGCACTCACACATGGAGTCACGAATTTCTACCCTCTTTGTCTAATGAAGAAATAGTCGCTCAGATCGAATGGTCAATCTGGGCTATGAACGCTACGGGAAAACATTTCCCCAAGTATTTTAGACCTCCTTACGGTGCCATAGACAATAGGGTTAGAGCTATTGTTAAACAGTTTGGATTGACCGTTGTGCTTTGGGACTTAGATACGTTTGATTGGAAGTTGATAACTAACGACGATTTCAGAACTGAGGAGGAAATCCTTATGGATATCAATACCTGGAAAGGCAAACGTAAGGGTTTAATATTAGAACACGACGGTGCTAGGAGAACGGTAGAGGTTGCTATAAAGATCAATGAACTAATCGGATCAGACCAGCTTACTATTGCTGAATGTATCGGAGATACCGACTACATAGAAAGGTACGAT</t>
+  </si>
+  <si>
+    <t>GCCGCTACTAAGACCCCTTTCCCTGACTGGCTGTCAGCATTCACAGGTCTGAAAGAGTGGCCTGGTTTGGATCCTCCATACATCCCTTTGGATTTTATTGATTTTTCCCAGATCCCCGATTACAAGGAATACGATCAAAATCATTGTGACTCTGTGCCTCGTGATTCTTGCTCTTTCGATTGTCATCATTGCACCGAACATGATGATGTTTACACTTGCTCAAAGTTGTCTCAAACATTTGACGACGGTCCTTCCGCATCCACTACAAAACTGCTGGACAGATTGAAGCACAACTCTACTTTTTTCAATTTGGGTGTAAATATCGTTCAACATCCAGACATTTATCAGAGGATGCAGAAGGAGGGTCATTTGATCGGATCTCACACTTGGTCCCACGTTTACCTGCCTAACGTTTCAAACGAAAAAATCATAGCCCAGATTGAGTGGTCTATTTGGGCAATGAATGCAACCGGTAATCATACTCCAAAGTGGTTTCGTCCCCCTTATGGTGGTATAGATAATAGAGTTCGTGCTATTACGAGACAATTTGGATTACAGGCCGTTCTTTGGGACCATGATACCTTTGACTGGTCCCTACTGTTGAATGACTCTGTGATCACCGAGCAAGAGATATTGCAGAACGTTATAAACTGGAATAAGTCTGGTACTGGACTGATATTAGAGCATGATTCTACTGAAAAGACAGTCGACTTAGCTATAAAGATTAATAAATTGATTGGTGATGATCAGAGTACAGTGAGTCACTGCGTCGGTGGAATAGATTACATTAAGGAGTTCCTTTCC</t>
+  </si>
+  <si>
+    <t>GACACATCCGCCAATTATTGGCAAAGTTTTACTAGTCAAATAAACCCCAAAAATATCAGTATCCCATCTATTGAACAAACTAGTTCCATTGATCCAACTCAAGAATGTGCTTATTACACACCTGATGCTTCTCTTTTTACCTTTAACGCATCTGAATGGCCTTCCATTTGGGAGGTTGCTACTACTAATGGAATGAACGAGAGTGCAGAATTCCTGTCTGTTTATAATTCCATCGACTGGACAAAAGCTCCAAACATAAGTGTTAGGACCTTGGATGCAAACGGTAACTTAGATACGACCGGCTACAATACAGCCACTGATCCCGACTGTTGGTGGACGGCCACCACCTGTACCAGTCCTAAAATTTCTGACATAAATGACGATATCTCCAAATGTCCTGAGCCAGAGACTTGGGGACTTACCTATGACGACGGACCCAATTGTTCACACAATGCTTTTTACGACTACCTGCAAGAACAAAAATTGAAGGCTTCTATGTTTTATATTGGCTCTAATGTTGTTGACTGGCCATACGGTGCAATGAGAGGTGTTGTCGATGGTCATCATATTGCTTCCCACACTTGGTCACACCCTCAAATGACTACAAAAACAAACCAAGAGGTGCTTGCTGAGTTTTACTACACTCAAAAAGCCATTAAACTTGCTACAGGACTGACCCCAAGGTACTGGCGTCCTCCATACGGTGATATTGATGACAGGGTCAGATGGATCGCCTCCCAGCTAGGTCTTACGGCCGTCATTTGGAATTTAGATACCGATGACTGGTCCGCAGGTGTGACAACCACTGTCGAGGCCGTTGAACAGAGTTACTCTGATTATATTGCTATGGGAACTAACGGCACCTTTGCTAACTCCGGAAATATCGTTCTTACGCACGAAATCAATACAACTATGTCCCTTGCTGTAGAAAATTTACCTAAAATCATCTCTGCATATAAGCAAGTAATTGATGTTGCCACTTGTTATAACATTTCTCACCCTTACTTTGAGGATTATGAGTGGACTAACGTGTTGAACGGCACTAAAAGTTCCGCCACGGCATCCGGTTCTGCCACTTCTGCCTCTGCAAGTGGTGGAGCTACAACA</t>
+  </si>
+  <si>
+    <t>GCTCCTACAAATGAAAAGCGTCAACAAGCTCAAGTTATATACGGCTGTACCCAACCAAATACCGTTGCTTTGACCTTTGATGATGGTCCCTATTGGTACATCTATGATATCTCAAATGCATTGACCTCAAGAGGCGCTAAGGGAACTTTCTTTTTCTCCGGTAATAACTATCAAAGAATTTACGACCAGGGAGCTATAGACCAGATTAAATATGCATATAACGCCGGACATCAGGTTGCCTCTCACACTTGGGGACATAAGGATTTAACTAGTTTGACATGGGACCAAATACACGACGAAATGTGGAGAGTCGAGTTAGCCTTGCAGAGAATTGTGGGCGTTCAGCCCGCTTTCATGCGTCCTCCCTATGGAAACTATGACGATGAGGTATTGTATGCTTCTTATATAAGGGGCCAGAAAGTAGTGATTTGGGATTTCGATTCTGGAGACTCAGTGGGAGCTTCTGCTGCTGAGAGTAAAGAAAGATATAGGACAACTAGTTTGAATAGACCCTCAACTTTGTTGGCATTGAACCACGAAACTATCGAGTCAACAGCACACGACGTAATTCCCTATGCAATCGATCGTCTACAAAGTGCAGGATATAGACTTGTTACCGTGGCAGAGTGTCTTGGAGAACAACCTTACCAATGGACTGGTGCTCCCCAGACGCCAACATCAGATTGGAGATGT</t>
+  </si>
+  <si>
+    <t>TCACCTATCCAAGAGAGACAATCATCAGTTCCAGTGGGAACCATAATCACCGCTTGTACTGTTCCAAATACTTTTGCTTTAACATTTGACGACGGTCCCTTCGCTTACACGTCTGAACTATTAGATCTGCTATCTTCTAATGGTGTTAAGGCTACTTTCTTCTTGAACGGCCAAAATTGGGGATCCATCTATGACTATACCTCTGTCGTCACCAGAATGGATGCTGAAGGTCACCAAATTGGATCACATACGTGGTCTCATGCCGACTTGGCAACTCTAGATGCTGCTGGAATTACTTCACAGATGACTCAGCTTGAGACTGCATTGACTTCCATCCTGGGTAAAGTTCCTACTTATATGCGTCCACCATACTTCTCAACTAATGCTTTAGCTCTGTCTACACTGGGTGGATTAGGATACCACGTCATCAACGCTAACATCGACACATTGGATTACGAACATGATGATGATACTATCGGTGTCGCATTTACCAACTTCCAAAATGGCCTGGCATCAGGTGGTACCGTCTCCCTGATGCACGATGTTCACGCTCAAACCGTCCACGTTCTAGTCCAGGAAGCCATTAACGCTATTAAGGCTAAAGGTTTGACACCAGTGACAGTTGGAACTTGCCTTGGTGATGCTTCTGCAAATTGGTATAAGTCCGGCGGTGGCAGTGGAACCACTCCACCTCCAGCTACTGGAGGACCCTCCCCAGACGATACATGTGGCGGTTCCAACGGCTACGTTTGTCAGAACTCACAGTGTTGTTCCCAATGGGGTTGGTGCGGAACCACATCTGAATACTGTGCTGCCGGTTGTCAAGCTGCATACGGTCCTTGCACG</t>
+  </si>
+  <si>
+    <t>TATAACTTGATCTGTTACTTTACAAACTGGGCTCAGTATAGACCAGGCTTGGGCTCCTTTAAGCCAGATGATATTAATCCTTGTCTATGTACTCATCTAATTTACGCCTTTGCTGGAATGCAGAACAATGAGATTACAACCATTGAATGGAACGATGTTACCTTATACAAAGCATTTAATGACTTGAAAAATAGGAACTCTAAACTTAAAACCTTACTAGCAATTGGTGGTTGGAATTTTGGTACTGCTCCATTCACGACAATGGTTTCCACCTCCCAAAACAGACAAACCTTTATTACTTCAGTTATCAAATTCCTGAGACAGTACGGATTTGATGGTTTAGACCTGGATTGGGAGTATCCTGGTTCTCGTGGTTCCCCTCCTCAAGACAAGCACCTTTTCACCGTCTTGGTTAAGGAAATGAGAGAAGCCTTTGAGCAAGAGGCTATTGAATCAAATAGACCAAGGCTTATGGTCACTGCAGCAGTTGCCGGAGGAATCTCTAATATTCAGGCTGGTTACGAGATCCCTGAATTGTCTAAGTACCTAGATTTTATCCACGTGATGACCTACGACTTGCATGGTTCATGGGAAGGATATACGGGCGAAAATAGTCCTCTGTATAAATACCCTACAGAAACAGGTTCCAACGCTTATTTGAACGTAGATTACGTTATGAATTATTGGAAAAACAACGGTGCTCCTGCTGAGAAATTGATAGTCGGTTTTCCTGAATATGGTCATACATTTATTTTGAGGAATCCATCCGATAATGGTATTGGCGCACCAACATCAGGTGACGGTCCAGCAGGACCATATACCCGTCAAGCCGGCTTCTGGGCTTATTATGAAATATGTACCTTCTTGAGATCTGGTGCAACCGAGGTCTGGGATGCATCTCAGGAGGTTCCTTACGCTTACAAGGCAAATGAGTGGCTTGGCTACGATAATATCAAGAGTTTTTCTGTTAAAGCTCAATGGCTAAAGCAAAATAATTTTGGAGGAGCTATGATATGGGCTATTGATTTGGATGATTTTACTGGATCCTTTTGTGATCAAGGTAAATTCCCATTGACCTCAACTTTGAACAAGGCATTAGGCATTAGTACTGAAGGTTGTACGGCACCTGATGTACCCAGTGAACCCGTTACTACTCCACCAGGATCTGGTTCCGGAGGAGGTTCCTCTGGTGGATCTTCAGGAGGTTCTGGTTTCTGTGCTGATAAAGCCGATGGCCTGTACCCCGTCGCTGACGACCGTAACGCCTTTTGGCAATGTATAAATGGTATAACTTATCAGCAACATTGTCAGGCTGGACTTGTGTTCGACACCAGTTGTAACTGCTGTAATTGGCCT</t>
+  </si>
+  <si>
+    <t>TCAAACATAGCTGCCTATTGGGGCCAAAATGCAGGCGGTGACCAGCAAACCCTGGGTGATTACTGTTCATCTTCACCTGCATCTATCATTATCCTGTCCTTCCTTGATGGATTTCCTAATTTGTCATTGAATTTCGCAAACCAATGCTCCGGCACTTTTAGTTCCGGCCTAGCTCACTGTTCTCAAATTGGTTCAGATATCAAATCTTGTCAACAACAGGGTAAAACCATCCTTCTATCATTGGGTGGTGCAACTGGTAATTATGGCTTCTCCTCTGACTCAGAAGCCGTCCAGTTTGCAGGTACGCTATGGAACAAGTTCGGAGGAGGTAAGGATAGTGAAAGACCATTTGATGATGCAATCGTAGATGGTTTTGATTTTGATATAGAAAACAAGGATCAAACTGGATATGCCGCTTTAGCAACTCAGTTGAGAAAGTACTTCTCCACCGGCACTAAGTCTTACTACTTGTCAGCCGCCCCACAATGTCCTTACCCTGACGAATCTGTGGGTGATTTGATGTCTCAAGTTGACCTGGATTTCGCCTTCATACAGTTTTACAATAACTACTGTTCACTGAATCAGCAGTTTAATTGGAATAGTTGGTCTAACTATGCTAGGGGAAAATCCATTAAATTATATTTGGGTTTGCCAGGAAGTTCATCCTCCGCCGGATCTGGTTTTGTCGGATTGTCCACTGTCCAAAGAGTAGTCGCTTCCATCAAGGGTGATTCTTCATTCGGAGGTATCTCTATCTGGGACATCTCCTCCGCTGAAAACGGCGGCTATCTGAATCAGCTTTATCAAGCTCTTAGTGGTTCTGGTTCTCCTGCTGCCCCCAGTAATAGTTACCAGCCCAACACGCCTTTGACACGTACCTACGGTGGCTCTACCGCTACAGCTTCCGCCTATATCTCAGTAGGTTTTACGGCCGGTGCTACGCACGGTAGTACCACTACCAACGACTTGTTGGCCTGGATTGATTCTTTATTTGGTTCTTCCCAGTCTTCTGTACAACAATATGCAACCCCCGTTCAAAGTGTTACGGCTACTCCACAACCCGTCGCCGCAACGACGACATCTGCTCCTAAGCCTACTGCCTCTGCTTTCAATTGGTTTGGTTGGTTCGACGGTACTACTACCTCTACTACTTTGCAAACGGTCTACTCAACTGTTCCCGCTGATCAAACTGTTTACGTTACGCTGACGACTACAGTCGGTAGTCAAATGTTGCAGTCCTTGTTTGACAAGAGAGATGTAATAGCCGAGGCTAAAAGTACTAACCTGCAAATTTGCTGGCTGTTGTTTATTCCTTTGTTGGCTTTAATCTGCTCA</t>
+  </si>
+  <si>
+    <t>CAAGGAGTCGGTAGTATTGTTACTAAGCCACTTTTCGACGAGATGCTGAAGCACCGTAACGACGCAAATTGTGCTTCAGGTTTCTATACATATGAAGCTTTCATCCAAGCCGCAAACTCTTTCGCCGCCTTTGGAACCGCCGGTGACGTTGACACTCGTAAAAGAGAGATTGCCGCTTTTTTGGCTCAGACTTCCCATGAAACTACTGGTGGATGGGCCACTGCTCCAGACGGTCCCTATGCTTGGGGATATTGTTTTAAACAAGAACAAGGTAATCCTCCTGATTATTGCCAAGCTTCTCAAGAGTGGCCTTGTGCCCCTGGTAAGAAATACTTTGGTAGAGGTCCTATACAAATTAGTTACAACTTCAATTATGGCCCTGCCGGTAAAGCTATTGGAAGTGATTTATTAAATAATCCAGATTTGGTAGCTACCGATCCAGTTATATCTTTTAAAACTGCTTTTTGGTTCTGGATGACACCACAATCTCCTAAACCCTCCGCTCATGCTGTTATGACTGGTGGTTGGACTCCTTCAGCTGCCGATACCGCTGCTGGTCGTGTCCCCGGATACGGTGTTGTTACTAATATCATCAACGGCGGTATTGAGTGTGGAAAAGGTTCTAACCCACAAATGGAAGACAGGATCGGATTTTATAAGAGGTACTGCGATATTTTGGGAGTTGGATATGGTAATAACTTAGATTGTGCAAACCAACGTCCATTTGGTAGT</t>
+  </si>
+  <si>
+    <t>AGTACCCCCTCAAGTACGGGTGAAAACAACGGTTTTTATTACTCCTTCTGGACTGACGGTGGAGGAGATGTGACTTACACTAACGGTGACGCAGGTGCTTATACTGTTGAATGGTCTAATGTGGGCAACTTTGTCGGTGGCAAAGGTTGGAATCCAGGAAGTGCTCAGGACATCACTTATTCTGGTACATTCACTCCATCTGGCAACGGTTATTTGTCCGTATATGGTTGGACTACCGATCCACTAATCGAATACTATATAGTAGAATCCTATGGTGACTATAACCCAGGTTCTGGAGGTACCTACAAGGGCACAGTCACATCCGACGGTTCAGTTTATGATATTTACACTGCAACCAGAACTAATGCAGCTTCTATCCAAGGTACCGCTACGTTCACCCAATACTGGTCTGTTAGGCAAAACAAGAGAGTCGGTGGCACTGTCACAACTTCTAACCATTTTAATGCTTGGGCCAAATTGGGAATGAACCTTGGTACTCACAACTATCAGATTGTGGCAACAGAAGGCTATCAGAGTTCTGGTTCCAGTTCTATTACAGTACAA</t>
+  </si>
+  <si>
+    <t>CAGACCATTCAACCCGGTACAGGTTACAACAATGGATACTTTTACAGTTATTGGAACGACGGACATGGAGGAGTTACATACACAAATGGACCTGGAGGACAATTCAGTGTTAATTGGAGTAATTCTGGCAATTTTGTTGGTGGAAAAGGTTGGCAACCTGGTACTAAAAATAAGGTTATCAACTTCTCAGGTAGTTACAATCCTAACGGAAATTCCTATCTTTCCGTATATGGTTGGAGTAGAAACCCTCTTATTGAGTATTATATTGTCGAAAACTTTGGTACCTATAACCCATCCACCGGAGCTACTAAGTTGGGAGAGGTCACATCTGATGGATCTGTCTACGATATTTACAGAACTCAAAGGGTTAACCAACCATCTATCATCGGTACTGCCACATTTTACCAATACTGGTCTGTTAGAAGAAATCATAGAAGTTCCGGTTCAGTTAACACAGCTAACCATTTTAATGCTTGGGCCCAGCAAGGATTGACATTAGGAACGATGGATTATCAGATCGTTGCCGTAGAAGGTTACTTTAGTAGTGGCTCCGCATCAATTACCGTAAGT</t>
+  </si>
+  <si>
+    <t>GCTGAAGCTATTAACTATAACCAGGATTACATTGCCTCTGGTGCCAACGTGCAGTACTCCCCAAACATGGCAGCTGGTTCTTTTTCAATAAATTATAATACACAGGGAGATTTCGTTGTGGGTCTAGGATGGCAGCCCGGCGACGCTAACCCTATTACTTACTCTGGATCTTTTTCTGCATCCGGCGTGGGTATTCTGGCAGTCTATGGTTGGTCTACTAATCCCTTGGTTGAATACTACGTTATGGAAGTCCACGACGGCTACCAAACAGCTGGAACTCATAAGGGTACTGTTACCACTGATGGCGGCACCTACGACATTTGGGAGCACCAGCAGGTCAATCAACCATCTATCTTAGGCACATCCACTTTTAATCAGTACATTAGTATTAGGCAATCTCCACGTACTTCCGGTACCGTTACTGTGCAAAACCACTTTAACGCATGGGCCCAAGCTGGAATGAATCTGGGAACCTTAAATTATCAGGTTATGGCTGTCGAAAGTTGGTCCGGTTCCGGTTCCGGTCAGATAAGTCTGTCTAAAGGTACTGGAGGTGGTAGTACCACAACCACTCCCACCGGACCTACCTCAACCTCCACTGCTCCATCTTCTGGCGGTACTGGAGCTGCCCAGTGGGGACAGTGTGGAGGTATTGGTTGGACTGGCCCAACTACTTGCGTGGCACCTTACACTTGTAAATATGAGAACGCTTATTACAGTCAGTGCCAG</t>
+  </si>
+  <si>
+    <t>ACTCCCATCGAGCCTTTGGCAGATCATCCAAACGAGGCTTTCAACGAAACTGCTTTCAACGATTTGGTCGGTAGAAGTACACCCTCATCCACTGGCTATAATAACGGTTACTATTACTCCTTTTGGACAGACGGAGGTGGTGATGTGACGTATACAAACGGTAATGGTGGTTCCTACTCTGTGCAGTGGAGTAATGTTGGCAATTTTGTAGGCGGTAAGGGTTGGAACCCAGGTTCTTCACGTGCTATCACTTACTCTGGATCATTCAACCCTAGTGGTAATGGATATTTGGCCGTTTACGGTTGGACTACTGACCCTCTGATTGAGTACTACATCGTTGAAAGTTACGGAACGTACAACCCTGGTTCAGGCGGAACCTACAAGGGTCAAGTTACTTCCGACGGTGGTACTTATAATATATACACTTCCGTTAGAACTAACGCTCCTTCTATCATAGGTACAGCCACTTTCACTCAATTCTGGTCTGTCAGAACTTCAAAGAGGGTTGGCGGAACTGTGACAACTGGTAACCATTTCAACGCTTGGGCCAAGTATGGTTTGACCTTGGGAACTCATAATTATCAAATTGTGGCTACTGAGGGATACCAATCTTCCGGTTCTTCTGCTATCACAGTTTAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAGACTACACCAAATTCTGAGGGTTGGCATGATGGATACTACTACAGTTGGTGGTCTGACGGTGGCGCTCAAGCCACCTACACTAATTTGGAAGGTGGCACATACGAAATCTCCTGGGGCGATGGCGGAAACCTAGTAGGTGGAAAGGGTTGGAACCCAGGTCTAAACGCTCGTGCTATCCACTTTGAAGGAGTTTACCAGCCTAACGGTAACTCCTATTTGGCTGTTTATGGATGGACTAGAAATCCTTTGGTTGAGTACTATATCGTTGAAAACTTTGGTACATACGACCCATCAAGTGGTGCTACTGACTTGGGAACCGTAGAATGTGATGGATCTATATATAGACTTGGTAAGACAACTAGAGTGAATGCTCCTTCAATCGATGGAACTCAAACATTCGACCAATATTGGTCAGTAAGACAAGATAAAAGAACTTCAGGTACCGTCCAAACAGGATGTCATTTTGATGCCTGGGCCAGAGCTGGTCTAAACGTGAACGGTGACCACTATTACCAGATAGTTGCAACCGAAGGATACTTTTCCTCTGGATACGCCAGAATTACCGTCGCTGATGTGGGT
+</t>
+  </si>
+  <si>
+    <t>F54_BpCDA</t>
+  </si>
+  <si>
+    <t>F55_SpCDA</t>
+  </si>
+  <si>
+    <t>F56_CfCDA</t>
+  </si>
+  <si>
+    <t>F57_EsCDA</t>
+  </si>
+  <si>
+    <t>F58_ReChitinase</t>
+  </si>
+  <si>
+    <t>F59_ClCDA</t>
+  </si>
+  <si>
+    <t>F60_MmCAR</t>
+  </si>
+  <si>
+    <t>F61_NcCAR</t>
+  </si>
+  <si>
+    <t>F62_ScCDA1</t>
+  </si>
+  <si>
+    <t>F63_ScCDA2</t>
+  </si>
+  <si>
+    <t>F64_MrCDA</t>
+  </si>
+  <si>
+    <t>F65_FvCDA</t>
+  </si>
+  <si>
+    <t>F66_PxCDA</t>
+  </si>
+  <si>
+    <t>F67_AmChitinase</t>
+  </si>
+  <si>
+    <t>F68_CaChitinase</t>
+  </si>
+  <si>
+    <t>F69_OsChitinase</t>
+  </si>
+  <si>
+    <t>F70_IbChitinase</t>
+  </si>
+  <si>
+    <t>F71_AnXylanase</t>
+  </si>
+  <si>
+    <t>F72_TrXylanase</t>
+  </si>
+  <si>
+    <t>F73_PfXylanase</t>
+  </si>
+  <si>
+    <t>F74_AoXylanase</t>
+  </si>
+  <si>
+    <t>F75_TlXylanase</t>
   </si>
 </sst>
 </file>
@@ -444,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C97CFC4B-B821-0B4D-A2D6-68A917D3879E}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
@@ -462,14 +586,245 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" s="1">
+        <v>54</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>66</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>70</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>73</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
